--- a/storage/app/public/services/services.xlsx
+++ b/storage/app/public/services/services.xlsx
@@ -1,16 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28224"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B89600CB-132A-4652-9315-F57024375320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kunal\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="27">
   <si>
     <t>Sr.No.</t>
   </si>
@@ -51,43 +55,73 @@
     <t>Type</t>
   </si>
   <si>
-    <t>SITC OF "MARC (MONITORING, ACCESS, RECORDING AND CONTROL SYSTEM"</t>
-  </si>
-  <si>
     <t>Nos.</t>
   </si>
   <si>
     <t>MARC</t>
   </si>
   <si>
-    <t>Supply, Installation, Testing &amp; Commissioning of IP CCTV Camera: IP DOME (Indoor): IP DOME MicroDome Duo, 2 Sensor Camera, 10 Megapixel Total, Remote Focus &amp; Day/Night H.264/MJPEG, SNAPstream, 2 x 2560x1920, 2 x 8.0mm MP Lens, 2 x 3 Axis Gimbals, Surface mount, Indoor/Outdoor, IP66, IK-10,PoE should have UL, CE &amp; FCC Certified etc. all complete.</t>
-  </si>
-  <si>
-    <t>Supply, Installation, Testing &amp; Commissioning of IP CCTV Camera : IP DOME (Indoor): 2 Megapixel or more WDR 1080p, 3.3-12mm manual varifocal lens,30 fps, Megapixel H.264/MJPEG Day/Night Camera, 1920x1080, motorized IR cut filter, Compact, 12VDC/24VAC/PoE;IP66;IK 10 Housing should have UL, CE &amp; FCC Certified etc. all complete.</t>
-  </si>
-  <si>
-    <t>Supply, Installation, Testing &amp; Commissioning of IP CCTV Camera: IP BULLET :2 Megapixel or more1080p ,1920x1080, 30 fps, WDR, IR LED Array, Day/Night, 3-9mm Remote Focus, Remote Zoom P-Iris Lens, IP66, 12VDC/24VAC/PoE, PoE Powered Fant should have UL, CE &amp; FCC Certified etc. all complete.</t>
-  </si>
-  <si>
     <t>AP</t>
   </si>
   <si>
-    <t>Supply, Installation, Testing &amp; Commissioning of IP CCTV Camera :Panaromic Camera 12 Megapixel WDR &amp; Day/Night H.264/MJPEG Omni-Directional Camera, 4 x 2048x1536, 4 x 2.8mm MP Lens, Surface mount, Indoor/Outdoor, IP66, IK-10, PoE Powered Fan should have UL, CE &amp; FCC Certified etc. all complete.</t>
-  </si>
-  <si>
-    <t>Supply, Installation, Testing &amp; Commissioning of IP CCTV Monitoring, Recording &amp; Streaming System: Control Room Equipments: Server Storage NVR for Main Control Rooms- Enterprise Storage Server Suitable for Up to 256 Cameras with 24 HDD supports up to 96TB expandable to 288TB by adding storage bay, dual power supply. Intel high-performance quad-core 64 bit processor, Pluggable, 1+1 redundant power supplies optional, Network port with Gigabit Ethernet, support Ethernet port bind, load sharing, RAID &amp; recording management, system log, alarm handling, Support device discovery protocol,API way to communication with monitoring platform, stream media search and send protocol, Support integration with the third party software platform by API etc. all complete.</t>
-  </si>
-  <si>
-    <t>Supply, Installation, Testing &amp; Commissioning of IP CCTV Monitoring, Recording &amp; Streaming System: Control Room Equipments: VMS Software supporting upto 256 Cameras. Unlimited client access, PTZ Control, Remote Viewing, Remote Storage, Playback. Supports JPEG, AVI, WAV export formats, Hourly schedules, Email Notification. This includes Camera and Base licenses etc. all complete.</t>
-  </si>
-  <si>
-    <t>Supply, Installation, Testing &amp; Commissioning of IP CCTV Monitoring, Recording &amp; Streaming System: Hard Disk Special Surveillance 4TB 3.5" SATA HDD internal( For Servers) etc. all complete.</t>
+    <t>IT Infrastructure Services</t>
+  </si>
+  <si>
+    <t>Networking - Active/Passive</t>
+  </si>
+  <si>
+    <t>Data Migration - On Premises/Cloud</t>
+  </si>
+  <si>
+    <t>Vitualisation</t>
+  </si>
+  <si>
+    <t>Data Center Management</t>
+  </si>
+  <si>
+    <t>Surviellance - Implementation &amp; Services</t>
+  </si>
+  <si>
+    <t>Cloud Services/Migration</t>
+  </si>
+  <si>
+    <t>IT Resources</t>
+  </si>
+  <si>
+    <t>Software &amp; Application Development</t>
+  </si>
+  <si>
+    <t>Mobile Application Development</t>
+  </si>
+  <si>
+    <t>Cyber Security - Implementation/Audits</t>
+  </si>
+  <si>
+    <t>IT Support &amp; Management Services</t>
+  </si>
+  <si>
+    <t>IOT and Physical Security</t>
+  </si>
+  <si>
+    <t>AI/ML</t>
+  </si>
+  <si>
+    <t>Training/Capacity Building</t>
+  </si>
+  <si>
+    <t>Compliance &amp; Advisory - DPDP Act Lifecycle</t>
+  </si>
+  <si>
+    <t>Data Center Sustainability - Net Zero</t>
+  </si>
+  <si>
+    <t>Industry 4.0 - Advisory/Implementation Services</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -537,15 +571,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="80.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="80.69921875" customWidth="1"/>
+    <col min="3" max="3" width="13.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="14.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -569,8 +603,8 @@
       <c r="A2" s="3">
         <v>102</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>6</v>
+      <c r="B2" t="s">
+        <v>9</v>
       </c>
       <c r="C2" s="4">
         <v>5598</v>
@@ -579,18 +613,18 @@
         <v>15</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="72">
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="3">
         <v>103</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
+      <c r="B3" t="s">
+        <v>10</v>
       </c>
       <c r="C3" s="4">
         <v>5599</v>
@@ -599,18 +633,18 @@
         <v>9</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" t="s">
         <v>7</v>
       </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="72">
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="3">
         <v>104</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>10</v>
+      <c r="B4" t="s">
+        <v>11</v>
       </c>
       <c r="C4" s="4">
         <v>5600</v>
@@ -619,18 +653,18 @@
         <v>266</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
         <v>7</v>
       </c>
-      <c r="F4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="57">
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="7">
         <v>105</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>11</v>
+      <c r="B5" t="s">
+        <v>12</v>
       </c>
       <c r="C5" s="8">
         <v>5601</v>
@@ -639,17 +673,17 @@
         <v>19</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="57">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="3">
         <v>106</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="4">
@@ -659,17 +693,17 @@
         <v>3</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="143.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="3">
         <v>107</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="4">
@@ -679,17 +713,17 @@
         <v>4</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
         <v>7</v>
       </c>
-      <c r="F7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="72">
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="3">
         <v>108</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="4">
@@ -699,17 +733,17 @@
         <v>4</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="42.75">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="3">
         <v>109</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="4">
@@ -719,10 +753,210 @@
         <v>96</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3">
+        <v>110</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="4">
+        <v>5606</v>
+      </c>
+      <c r="D10" s="4">
+        <v>15</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3">
+        <v>111</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="4">
+        <v>5607</v>
+      </c>
+      <c r="D11" s="4">
+        <v>9</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3">
+        <v>112</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="4">
+        <v>5608</v>
+      </c>
+      <c r="D12" s="4">
+        <v>266</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7">
+        <v>113</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="8">
+        <v>5609</v>
+      </c>
+      <c r="D13" s="8">
+        <v>19</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3">
+        <v>114</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="4">
+        <v>5610</v>
+      </c>
+      <c r="D14" s="4">
+        <v>3</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3">
+        <v>115</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="4">
+        <v>5611</v>
+      </c>
+      <c r="D15" s="4">
+        <v>4</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3">
+        <v>116</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="4">
+        <v>5612</v>
+      </c>
+      <c r="D16" s="4">
+        <v>4</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="3">
+        <v>117</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="4">
+        <v>5613</v>
+      </c>
+      <c r="D17" s="4">
+        <v>96</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="3">
+        <v>118</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="4">
+        <v>5614</v>
+      </c>
+      <c r="D18" s="4">
+        <v>96</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="3">
+        <v>119</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="4">
+        <v>5615</v>
+      </c>
+      <c r="D19" s="4">
+        <v>96</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
